--- a/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>RCON</t>
   </si>
@@ -758,8 +758,8 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>40</v>
+      <c r="D8" s="3">
+        <v>3000</v>
       </c>
       <c r="E8" s="3">
         <v>6300</v>
@@ -768,10 +768,10 @@
         <v>4100</v>
       </c>
       <c r="G8" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="H8" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="I8" s="3">
         <v>3500</v>
@@ -820,8 +820,8 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>40</v>
+      <c r="D9" s="3">
+        <v>2200</v>
       </c>
       <c r="E9" s="3">
         <v>4500</v>
@@ -836,10 +836,10 @@
         <v>3100</v>
       </c>
       <c r="I9" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="J9" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K9" s="3">
         <v>2500</v>
@@ -882,8 +882,8 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
+      <c r="D10" s="3">
+        <v>800</v>
       </c>
       <c r="E10" s="3">
         <v>1800</v>
@@ -969,7 +969,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E12" s="3">
         <v>700</v>
@@ -1092,8 +1092,8 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>40</v>
+      <c r="D14" s="3">
+        <v>1500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>40</v>
@@ -1237,8 +1237,8 @@
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>40</v>
+      <c r="D17" s="3">
+        <v>11900</v>
       </c>
       <c r="E17" s="3">
         <v>8400</v>
@@ -1247,13 +1247,13 @@
         <v>10600</v>
       </c>
       <c r="G17" s="3">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="H17" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="I17" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="J17" s="3">
         <v>6700</v>
@@ -1299,20 +1299,20 @@
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>40</v>
+      <c r="D18" s="3">
+        <v>-8900</v>
       </c>
       <c r="E18" s="3">
         <v>-2100</v>
       </c>
       <c r="F18" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="G18" s="3">
         <v>-5200</v>
       </c>
       <c r="H18" s="3">
-        <v>-7200</v>
+        <v>-7300</v>
       </c>
       <c r="I18" s="3">
         <v>-1300</v>
@@ -1385,8 +1385,8 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>40</v>
+      <c r="D20" s="3">
+        <v>4900</v>
       </c>
       <c r="E20" s="3">
         <v>-2000</v>
@@ -1395,7 +1395,7 @@
         <v>4200</v>
       </c>
       <c r="G20" s="3">
-        <v>20700</v>
+        <v>20800</v>
       </c>
       <c r="H20" s="3">
         <v>5200</v>
@@ -1447,17 +1447,17 @@
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>40</v>
+      <c r="D21" s="3">
+        <v>-3800</v>
       </c>
       <c r="E21" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="F21" s="3">
         <v>-2100</v>
       </c>
       <c r="G21" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="H21" s="3">
         <v>-1800</v>
@@ -1572,19 +1572,19 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-8500</v>
+        <v>-4400</v>
       </c>
       <c r="E23" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="F23" s="3">
         <v>-2500</v>
       </c>
       <c r="G23" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H23" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="I23" s="3">
         <v>-1400</v>
@@ -1757,17 +1757,17 @@
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>40</v>
+      <c r="D26" s="3">
+        <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="F26" s="3">
         <v>-2400</v>
       </c>
       <c r="G26" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H26" s="3">
         <v>-2200</v>
@@ -1819,17 +1819,17 @@
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>40</v>
+      <c r="D27" s="3">
+        <v>-4100</v>
       </c>
       <c r="E27" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="F27" s="3">
         <v>-2200</v>
       </c>
       <c r="G27" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H27" s="3">
         <v>-1900</v>
@@ -2129,8 +2129,8 @@
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>40</v>
+      <c r="D32" s="3">
+        <v>-4900</v>
       </c>
       <c r="E32" s="3">
         <v>2000</v>
@@ -2139,7 +2139,7 @@
         <v>-4200</v>
       </c>
       <c r="G32" s="3">
-        <v>-20700</v>
+        <v>-20800</v>
       </c>
       <c r="H32" s="3">
         <v>-5200</v>
@@ -2191,17 +2191,17 @@
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>40</v>
+      <c r="D33" s="3">
+        <v>-4100</v>
       </c>
       <c r="E33" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="F33" s="3">
         <v>-2200</v>
       </c>
       <c r="G33" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H33" s="3">
         <v>-1900</v>
@@ -2315,17 +2315,17 @@
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>40</v>
+      <c r="D35" s="3">
+        <v>-4100</v>
       </c>
       <c r="E35" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="F35" s="3">
         <v>-2200</v>
       </c>
       <c r="G35" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H35" s="3">
         <v>-1900</v>
@@ -2493,19 +2493,19 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>14400</v>
+        <v>14500</v>
       </c>
       <c r="E41" s="3">
-        <v>37200</v>
+        <v>37400</v>
       </c>
       <c r="F41" s="3">
-        <v>43800</v>
+        <v>44100</v>
       </c>
       <c r="G41" s="3">
-        <v>46000</v>
+        <v>46300</v>
       </c>
       <c r="H41" s="3">
-        <v>47500</v>
+        <v>47800</v>
       </c>
       <c r="I41" s="3">
         <v>9800</v>
@@ -2555,7 +2555,7 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>25400</v>
+        <v>25600</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>40</v>
@@ -2617,25 +2617,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>21600</v>
+        <v>28600</v>
       </c>
       <c r="E43" s="3">
-        <v>23900</v>
+        <v>24100</v>
       </c>
       <c r="F43" s="3">
+        <v>17100</v>
+      </c>
+      <c r="G43" s="3">
         <v>17000</v>
       </c>
-      <c r="G43" s="3">
-        <v>16800</v>
-      </c>
       <c r="H43" s="3">
-        <v>19200</v>
+        <v>19400</v>
       </c>
       <c r="I43" s="3">
-        <v>13900</v>
+        <v>14000</v>
       </c>
       <c r="J43" s="3">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="K43" s="3">
         <v>12400</v>
@@ -2741,7 +2741,7 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
@@ -2803,25 +2803,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>69600</v>
+        <v>70100</v>
       </c>
       <c r="E46" s="3">
-        <v>62000</v>
+        <v>62400</v>
       </c>
       <c r="F46" s="3">
-        <v>61500</v>
+        <v>61900</v>
       </c>
       <c r="G46" s="3">
-        <v>63600</v>
+        <v>64000</v>
       </c>
       <c r="H46" s="3">
-        <v>67500</v>
+        <v>67900</v>
       </c>
       <c r="I46" s="3">
-        <v>24000</v>
+        <v>24200</v>
       </c>
       <c r="J46" s="3">
-        <v>17900</v>
+        <v>18000</v>
       </c>
       <c r="K46" s="3">
         <v>14100</v>
@@ -2880,7 +2880,7 @@
         <v>3900</v>
       </c>
       <c r="I47" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="J47" s="3">
         <v>4400</v>
@@ -2927,19 +2927,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="E48" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="F48" s="3">
         <v>4300</v>
       </c>
       <c r="G48" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="H48" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="I48" s="3">
         <v>4300</v>
@@ -2988,8 +2988,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>40</v>
+      <c r="D49" s="3">
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>1400</v>
@@ -3299,25 +3299,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>73400</v>
+        <v>73900</v>
       </c>
       <c r="E54" s="3">
+        <v>68700</v>
+      </c>
+      <c r="F54" s="3">
         <v>68200</v>
       </c>
-      <c r="F54" s="3">
-        <v>67700</v>
-      </c>
       <c r="G54" s="3">
-        <v>70100</v>
+        <v>70500</v>
       </c>
       <c r="H54" s="3">
-        <v>78200</v>
+        <v>78800</v>
       </c>
       <c r="I54" s="3">
-        <v>32800</v>
+        <v>33000</v>
       </c>
       <c r="J54" s="3">
-        <v>26800</v>
+        <v>27000</v>
       </c>
       <c r="K54" s="3">
         <v>22400</v>
@@ -3412,16 +3412,16 @@
         <v>1500</v>
       </c>
       <c r="E57" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="F57" s="3">
         <v>2300</v>
       </c>
       <c r="G57" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="H57" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="I57" s="3">
         <v>2700</v>
@@ -3486,7 +3486,7 @@
         <v>4000</v>
       </c>
       <c r="I58" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="J58" s="3">
         <v>2900</v>
@@ -3533,7 +3533,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
         <v>1900</v>
@@ -3551,7 +3551,7 @@
         <v>2800</v>
       </c>
       <c r="J59" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="K59" s="3">
         <v>2900</v>
@@ -3595,25 +3595,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="E60" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="F60" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="G60" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="H60" s="3">
         <v>10600</v>
       </c>
       <c r="I60" s="3">
-        <v>14800</v>
+        <v>14900</v>
       </c>
       <c r="J60" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="K60" s="3">
         <v>7000</v>
@@ -3722,7 +3722,7 @@
         <v>4400</v>
       </c>
       <c r="E62" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="F62" s="3">
         <v>2600</v>
@@ -3731,7 +3731,7 @@
         <v>6400</v>
       </c>
       <c r="H62" s="3">
-        <v>27100</v>
+        <v>27300</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
@@ -3967,22 +3967,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="E66" s="3">
-        <v>12100</v>
+        <v>12200</v>
       </c>
       <c r="F66" s="3">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G66" s="3">
-        <v>14000</v>
+        <v>14100</v>
       </c>
       <c r="H66" s="3">
-        <v>37500</v>
+        <v>37700</v>
       </c>
       <c r="I66" s="3">
-        <v>17100</v>
+        <v>17200</v>
       </c>
       <c r="J66" s="3">
         <v>11700</v>
@@ -4301,25 +4301,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-23000</v>
+        <v>-23100</v>
       </c>
       <c r="E72" s="3">
-        <v>-18900</v>
+        <v>-19000</v>
       </c>
       <c r="F72" s="3">
-        <v>-14800</v>
+        <v>-14900</v>
       </c>
       <c r="G72" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="H72" s="3">
-        <v>-28000</v>
+        <v>-28200</v>
       </c>
       <c r="I72" s="3">
-        <v>-26100</v>
+        <v>-26200</v>
       </c>
       <c r="J72" s="3">
-        <v>-24800</v>
+        <v>-25000</v>
       </c>
       <c r="K72" s="3">
         <v>-23100</v>
@@ -4549,25 +4549,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>62000</v>
+        <v>62400</v>
       </c>
       <c r="E76" s="3">
-        <v>56100</v>
+        <v>56500</v>
       </c>
       <c r="F76" s="3">
-        <v>58100</v>
+        <v>58500</v>
       </c>
       <c r="G76" s="3">
-        <v>56100</v>
+        <v>56500</v>
       </c>
       <c r="H76" s="3">
-        <v>40700</v>
+        <v>41000</v>
       </c>
       <c r="I76" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="J76" s="3">
-        <v>15200</v>
+        <v>15300</v>
       </c>
       <c r="K76" s="3">
         <v>12800</v>
@@ -4739,17 +4739,17 @@
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>40</v>
+      <c r="D81" s="3">
+        <v>-4100</v>
       </c>
       <c r="E81" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="F81" s="3">
         <v>-2200</v>
       </c>
       <c r="G81" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H81" s="3">
         <v>-1900</v>
@@ -4826,7 +4826,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -5198,7 +5198,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-7100</v>
+        <v>-3600</v>
       </c>
       <c r="E89" s="3">
         <v>-3600</v>
@@ -5470,13 +5470,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-33900</v>
+        <v>-29400</v>
       </c>
       <c r="E94" s="3">
         <v>-4700</v>
       </c>
       <c r="F94" s="3">
-        <v>-3700</v>
+        <v>-3800</v>
       </c>
       <c r="G94" s="3">
         <v>3700</v>
@@ -5804,7 +5804,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7800</v>
+        <v>7600</v>
       </c>
       <c r="E100" s="3">
         <v>200</v>
@@ -5816,13 +5816,13 @@
         <v>-1300</v>
       </c>
       <c r="H100" s="3">
-        <v>46600</v>
+        <v>47000</v>
       </c>
       <c r="I100" s="3">
         <v>7800</v>
       </c>
       <c r="J100" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="K100" s="3">
         <v>300</v>
@@ -5866,7 +5866,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3800</v>
+        <v>2400</v>
       </c>
       <c r="E101" s="3">
         <v>1500</v>
@@ -5927,11 +5927,11 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>40</v>
+      <c r="D102" s="3">
+        <v>-22900</v>
       </c>
       <c r="E102" s="3">
-        <v>-6600</v>
+        <v>-6700</v>
       </c>
       <c r="F102" s="3">
         <v>-2100</v>
@@ -5940,7 +5940,7 @@
         <v>-1500</v>
       </c>
       <c r="H102" s="3">
-        <v>37700</v>
+        <v>38000</v>
       </c>
       <c r="I102" s="3">
         <v>5600</v>

--- a/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
@@ -768,7 +768,7 @@
         <v>4100</v>
       </c>
       <c r="G8" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="H8" s="3">
         <v>3200</v>
@@ -836,10 +836,10 @@
         <v>3100</v>
       </c>
       <c r="I9" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="J9" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K9" s="3">
         <v>2500</v>
@@ -1247,13 +1247,13 @@
         <v>10600</v>
       </c>
       <c r="G17" s="3">
-        <v>12800</v>
+        <v>12700</v>
       </c>
       <c r="H17" s="3">
-        <v>10500</v>
+        <v>10400</v>
       </c>
       <c r="I17" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="J17" s="3">
         <v>6700</v>
@@ -1306,13 +1306,13 @@
         <v>-2100</v>
       </c>
       <c r="F18" s="3">
-        <v>-6600</v>
+        <v>-6500</v>
       </c>
       <c r="G18" s="3">
         <v>-5200</v>
       </c>
       <c r="H18" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="I18" s="3">
         <v>-1300</v>
@@ -1386,7 +1386,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
         <v>-2000</v>
@@ -1395,7 +1395,7 @@
         <v>4200</v>
       </c>
       <c r="G20" s="3">
-        <v>20800</v>
+        <v>20700</v>
       </c>
       <c r="H20" s="3">
         <v>5200</v>
@@ -1451,13 +1451,13 @@
         <v>-3800</v>
       </c>
       <c r="E21" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="F21" s="3">
         <v>-2100</v>
       </c>
       <c r="G21" s="3">
-        <v>15800</v>
+        <v>15700</v>
       </c>
       <c r="H21" s="3">
         <v>-1800</v>
@@ -1575,16 +1575,16 @@
         <v>-4400</v>
       </c>
       <c r="E23" s="3">
-        <v>-4200</v>
+        <v>-4100</v>
       </c>
       <c r="F23" s="3">
         <v>-2500</v>
       </c>
       <c r="G23" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="H23" s="3">
-        <v>-2300</v>
+        <v>-2200</v>
       </c>
       <c r="I23" s="3">
         <v>-1400</v>
@@ -1761,13 +1761,13 @@
         <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>-4200</v>
+        <v>-4100</v>
       </c>
       <c r="F26" s="3">
         <v>-2400</v>
       </c>
       <c r="G26" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="H26" s="3">
         <v>-2200</v>
@@ -1820,16 +1820,16 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-4200</v>
       </c>
       <c r="F27" s="3">
         <v>-2200</v>
       </c>
       <c r="G27" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="H27" s="3">
         <v>-1900</v>
@@ -2130,7 +2130,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-4900</v>
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
         <v>2000</v>
@@ -2139,7 +2139,7 @@
         <v>-4200</v>
       </c>
       <c r="G32" s="3">
-        <v>-20800</v>
+        <v>-20700</v>
       </c>
       <c r="H32" s="3">
         <v>-5200</v>
@@ -2192,16 +2192,16 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-4200</v>
       </c>
       <c r="F33" s="3">
         <v>-2200</v>
       </c>
       <c r="G33" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="H33" s="3">
         <v>-1900</v>
@@ -2316,16 +2316,16 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-4200</v>
       </c>
       <c r="F35" s="3">
         <v>-2200</v>
       </c>
       <c r="G35" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="H35" s="3">
         <v>-1900</v>
@@ -2493,19 +2493,19 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>14500</v>
+        <v>14400</v>
       </c>
       <c r="E41" s="3">
-        <v>37400</v>
+        <v>37200</v>
       </c>
       <c r="F41" s="3">
-        <v>44100</v>
+        <v>43800</v>
       </c>
       <c r="G41" s="3">
-        <v>46300</v>
+        <v>46000</v>
       </c>
       <c r="H41" s="3">
-        <v>47800</v>
+        <v>47500</v>
       </c>
       <c r="I41" s="3">
         <v>9800</v>
@@ -2555,7 +2555,7 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>25600</v>
+        <v>25400</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>40</v>
@@ -2617,25 +2617,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>28600</v>
+        <v>28500</v>
       </c>
       <c r="E43" s="3">
-        <v>24100</v>
+        <v>23900</v>
       </c>
       <c r="F43" s="3">
-        <v>17100</v>
+        <v>17000</v>
       </c>
       <c r="G43" s="3">
-        <v>17000</v>
+        <v>16900</v>
       </c>
       <c r="H43" s="3">
-        <v>19400</v>
+        <v>19200</v>
       </c>
       <c r="I43" s="3">
-        <v>14000</v>
+        <v>13900</v>
       </c>
       <c r="J43" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="K43" s="3">
         <v>12400</v>
@@ -2803,25 +2803,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>70100</v>
+        <v>69700</v>
       </c>
       <c r="E46" s="3">
-        <v>62400</v>
+        <v>62000</v>
       </c>
       <c r="F46" s="3">
-        <v>61900</v>
+        <v>61600</v>
       </c>
       <c r="G46" s="3">
-        <v>64000</v>
+        <v>63600</v>
       </c>
       <c r="H46" s="3">
-        <v>67900</v>
+        <v>67500</v>
       </c>
       <c r="I46" s="3">
-        <v>24200</v>
+        <v>24000</v>
       </c>
       <c r="J46" s="3">
-        <v>18000</v>
+        <v>17900</v>
       </c>
       <c r="K46" s="3">
         <v>14100</v>
@@ -2880,7 +2880,7 @@
         <v>3900</v>
       </c>
       <c r="I47" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="J47" s="3">
         <v>4400</v>
@@ -2930,16 +2930,16 @@
         <v>3800</v>
       </c>
       <c r="E48" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="F48" s="3">
         <v>4300</v>
       </c>
       <c r="G48" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="H48" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="I48" s="3">
         <v>4300</v>
@@ -3299,25 +3299,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>73900</v>
+        <v>73500</v>
       </c>
       <c r="E54" s="3">
-        <v>68700</v>
+        <v>68300</v>
       </c>
       <c r="F54" s="3">
-        <v>68200</v>
+        <v>67700</v>
       </c>
       <c r="G54" s="3">
-        <v>70500</v>
+        <v>70100</v>
       </c>
       <c r="H54" s="3">
-        <v>78800</v>
+        <v>78300</v>
       </c>
       <c r="I54" s="3">
-        <v>33000</v>
+        <v>32800</v>
       </c>
       <c r="J54" s="3">
-        <v>27000</v>
+        <v>26900</v>
       </c>
       <c r="K54" s="3">
         <v>22400</v>
@@ -3412,16 +3412,16 @@
         <v>1500</v>
       </c>
       <c r="E57" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="F57" s="3">
         <v>2300</v>
       </c>
       <c r="G57" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="H57" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="I57" s="3">
         <v>2700</v>
@@ -3486,7 +3486,7 @@
         <v>4000</v>
       </c>
       <c r="I58" s="3">
-        <v>9400</v>
+        <v>9300</v>
       </c>
       <c r="J58" s="3">
         <v>2900</v>
@@ -3551,7 +3551,7 @@
         <v>2800</v>
       </c>
       <c r="J59" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="K59" s="3">
         <v>2900</v>
@@ -3595,25 +3595,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8500</v>
+        <v>8400</v>
       </c>
       <c r="E60" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="F60" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="G60" s="3">
-        <v>7900</v>
+        <v>7800</v>
       </c>
       <c r="H60" s="3">
         <v>10600</v>
       </c>
       <c r="I60" s="3">
-        <v>14900</v>
+        <v>14800</v>
       </c>
       <c r="J60" s="3">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="K60" s="3">
         <v>7000</v>
@@ -3722,7 +3722,7 @@
         <v>4400</v>
       </c>
       <c r="E62" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="F62" s="3">
         <v>2600</v>
@@ -3731,7 +3731,7 @@
         <v>6400</v>
       </c>
       <c r="H62" s="3">
-        <v>27300</v>
+        <v>27100</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
@@ -3967,22 +3967,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="E66" s="3">
-        <v>12200</v>
+        <v>12100</v>
       </c>
       <c r="F66" s="3">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="G66" s="3">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="H66" s="3">
-        <v>37700</v>
+        <v>37500</v>
       </c>
       <c r="I66" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="J66" s="3">
         <v>11700</v>
@@ -4301,25 +4301,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-23100</v>
+        <v>-23000</v>
       </c>
       <c r="E72" s="3">
-        <v>-19000</v>
+        <v>-18900</v>
       </c>
       <c r="F72" s="3">
-        <v>-14900</v>
+        <v>-14800</v>
       </c>
       <c r="G72" s="3">
-        <v>-12700</v>
+        <v>-12600</v>
       </c>
       <c r="H72" s="3">
-        <v>-28200</v>
+        <v>-28000</v>
       </c>
       <c r="I72" s="3">
-        <v>-26200</v>
+        <v>-26100</v>
       </c>
       <c r="J72" s="3">
-        <v>-25000</v>
+        <v>-24900</v>
       </c>
       <c r="K72" s="3">
         <v>-23100</v>
@@ -4549,25 +4549,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>62400</v>
+        <v>62100</v>
       </c>
       <c r="E76" s="3">
-        <v>56500</v>
+        <v>56200</v>
       </c>
       <c r="F76" s="3">
-        <v>58500</v>
+        <v>58100</v>
       </c>
       <c r="G76" s="3">
-        <v>56500</v>
+        <v>56100</v>
       </c>
       <c r="H76" s="3">
-        <v>41000</v>
+        <v>40800</v>
       </c>
       <c r="I76" s="3">
-        <v>15800</v>
+        <v>15700</v>
       </c>
       <c r="J76" s="3">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="K76" s="3">
         <v>12800</v>
@@ -4740,16 +4740,16 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-4200</v>
       </c>
       <c r="F81" s="3">
         <v>-2200</v>
       </c>
       <c r="G81" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="H81" s="3">
         <v>-1900</v>
@@ -5470,13 +5470,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-29400</v>
+        <v>-29200</v>
       </c>
       <c r="E94" s="3">
         <v>-4700</v>
       </c>
       <c r="F94" s="3">
-        <v>-3800</v>
+        <v>-3700</v>
       </c>
       <c r="G94" s="3">
         <v>3700</v>
@@ -5816,13 +5816,13 @@
         <v>-1300</v>
       </c>
       <c r="H100" s="3">
-        <v>47000</v>
+        <v>46700</v>
       </c>
       <c r="I100" s="3">
         <v>7800</v>
       </c>
       <c r="J100" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="K100" s="3">
         <v>300</v>
@@ -5928,10 +5928,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-22900</v>
+        <v>-22800</v>
       </c>
       <c r="E102" s="3">
-        <v>-6700</v>
+        <v>-6600</v>
       </c>
       <c r="F102" s="3">
         <v>-2100</v>
@@ -5940,7 +5940,7 @@
         <v>-1500</v>
       </c>
       <c r="H102" s="3">
-        <v>38000</v>
+        <v>37700</v>
       </c>
       <c r="I102" s="3">
         <v>5600</v>

--- a/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>RCON</t>
   </si>
@@ -656,291 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>43190</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>43008</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>42916</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>42825</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>42735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>42643</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="E8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N8" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P8" s="3">
+        <v>8500</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T8" s="3">
         <v>6300</v>
       </c>
-      <c r="F8" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>7500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K8" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L8" s="3">
-        <v>8500</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2400</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>6300</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>1800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>2300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>4400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>1100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="S9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="U9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V9" s="3">
         <v>2200</v>
       </c>
-      <c r="E9" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>6500</v>
-      </c>
-      <c r="M9" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N9" s="3">
-        <v>2900</v>
-      </c>
-      <c r="O9" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P9" s="3">
-        <v>5700</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="R9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>3000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>1000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>900</v>
+      </c>
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F10" s="3">
-        <v>700</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>1600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>2100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>2100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>-600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>1400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -963,8 +1013,12 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,52 +1026,52 @@
         <v>500</v>
       </c>
       <c r="E12" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F12" s="3">
         <v>500</v>
       </c>
       <c r="G12" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3">
         <v>300</v>
       </c>
       <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>400</v>
+      </c>
+      <c r="K12" s="3">
+        <v>800</v>
+      </c>
+      <c r="L12" s="3">
+        <v>300</v>
+      </c>
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>100</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
       </c>
       <c r="Q12" s="3">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
         <v>200</v>
-      </c>
-      <c r="S12" s="3">
-        <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>600</v>
       </c>
       <c r="U12" s="3">
         <v>100</v>
@@ -1025,8 +1079,20 @@
       <c r="V12" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3">
+        <v>200</v>
+      </c>
+      <c r="X12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1087,28 +1153,40 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>1500</v>
+      <c r="D14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="3">
-        <v>300</v>
+      <c r="F14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H14" s="3">
-        <v>100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>800</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>40</v>
@@ -1116,8 +1194,8 @@
       <c r="K14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>40</v>
+      <c r="L14" s="3">
+        <v>100</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>40</v>
@@ -1125,17 +1203,17 @@
       <c r="N14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1149,31 +1227,43 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1211,8 +1301,20 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1232,132 +1334,160 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>11900</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="3">
-        <v>8400</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="3">
-        <v>10600</v>
+        <v>4800</v>
       </c>
       <c r="G17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K17" s="3">
         <v>12700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>6700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>10700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>7100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>4200</v>
-      </c>
-      <c r="P17" s="3">
-        <v>7900</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>2800</v>
       </c>
       <c r="R17" s="3">
         <v>4400</v>
       </c>
       <c r="S17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="T17" s="3">
+        <v>7900</v>
+      </c>
+      <c r="U17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>5000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-8900</v>
+        <v>-3400</v>
       </c>
       <c r="E18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1380,56 +1510,60 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>4800</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>-2000</v>
+        <v>-600</v>
       </c>
       <c r="F20" s="3">
-        <v>4200</v>
+        <v>700</v>
       </c>
       <c r="G20" s="3">
+        <v>700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="3">
         <v>20700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
         <v>5200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1442,75 +1576,99 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-3800</v>
+        <v>-2600</v>
       </c>
       <c r="E21" s="3">
-        <v>-3800</v>
+        <v>-2700</v>
       </c>
       <c r="F21" s="3">
-        <v>-2100</v>
+        <v>-2300</v>
       </c>
       <c r="G21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K21" s="3">
         <v>15700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>-1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>-1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1525,16 +1683,16 @@
         <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1543,16 +1701,16 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1566,34 +1724,46 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-4400</v>
+        <v>-2000</v>
       </c>
       <c r="E23" s="3">
-        <v>-4100</v>
+        <v>-2000</v>
       </c>
       <c r="F23" s="3">
-        <v>-2500</v>
+        <v>-1600</v>
       </c>
       <c r="G23" s="3">
-        <v>15400</v>
+        <v>-1600</v>
       </c>
       <c r="H23" s="3">
         <v>-2200</v>
       </c>
       <c r="I23" s="3">
-        <v>-1400</v>
+        <v>-2300</v>
       </c>
       <c r="J23" s="3">
-        <v>-1800</v>
+        <v>-2200</v>
       </c>
       <c r="K23" s="3">
-        <v>-900</v>
+        <v>15400</v>
       </c>
       <c r="L23" s="3">
         <v>-2200</v>
@@ -1602,34 +1772,46 @@
         <v>-1400</v>
       </c>
       <c r="N23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1640,38 +1822,38 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1690,8 +1872,20 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1752,132 +1946,168 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-4400</v>
+        <v>-1900</v>
       </c>
       <c r="E26" s="3">
-        <v>-4100</v>
+        <v>-2000</v>
       </c>
       <c r="F26" s="3">
-        <v>-2400</v>
+        <v>-1600</v>
       </c>
       <c r="G26" s="3">
-        <v>15400</v>
+        <v>-1600</v>
       </c>
       <c r="H26" s="3">
         <v>-2200</v>
       </c>
       <c r="I26" s="3">
-        <v>-1400</v>
+        <v>-2300</v>
       </c>
       <c r="J26" s="3">
-        <v>-1800</v>
+        <v>-2200</v>
       </c>
       <c r="K26" s="3">
-        <v>-1000</v>
+        <v>15400</v>
       </c>
       <c r="L26" s="3">
-        <v>-2300</v>
+        <v>-2200</v>
       </c>
       <c r="M26" s="3">
         <v>-1400</v>
       </c>
       <c r="N26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="R26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-4000</v>
+        <v>-1900</v>
       </c>
       <c r="E27" s="3">
-        <v>-4100</v>
+        <v>-1900</v>
       </c>
       <c r="F27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="K27" s="3">
         <v>15400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>-1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1938,8 +2168,20 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2000,8 +2242,20 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2316,20 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,56 +2390,68 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-4800</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="F32" s="3">
-        <v>-4200</v>
+        <v>-700</v>
       </c>
       <c r="G32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-20700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
         <v>-5200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2186,70 +2464,94 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-4000</v>
+        <v>-1900</v>
       </c>
       <c r="E33" s="3">
-        <v>-4100</v>
+        <v>-1900</v>
       </c>
       <c r="F33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="K33" s="3">
         <v>15400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2310,137 +2612,173 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-4000</v>
+        <v>-1900</v>
       </c>
       <c r="E35" s="3">
-        <v>-4100</v>
+        <v>-1900</v>
       </c>
       <c r="F35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="K35" s="3">
         <v>15400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>43190</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>43008</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>42916</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>42825</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>42735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>42643</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2463,8 +2801,12 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2487,106 +2829,122 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>17200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="H41" s="3">
         <v>14400</v>
       </c>
-      <c r="E41" s="3">
-        <v>37200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>43800</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J41" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K41" s="3">
         <v>46000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>47500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>9800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>4200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>7200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>1300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>18900</v>
+      </c>
+      <c r="G42" s="3">
+        <v>18400</v>
+      </c>
+      <c r="H42" s="3">
         <v>25400</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="I42" s="3">
+        <v>26800</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="N42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2611,70 +2969,94 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>28500</v>
+        <v>41400</v>
       </c>
       <c r="E43" s="3">
-        <v>23900</v>
+        <v>41700</v>
       </c>
       <c r="F43" s="3">
-        <v>17000</v>
+        <v>23200</v>
       </c>
       <c r="G43" s="3">
+        <v>22500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>28400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>30000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K43" s="3">
         <v>16900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>19200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>13900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>13300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>12400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>12800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>7400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>5600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>8400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>6800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>7100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>8600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>10500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>8800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2682,123 +3064,147 @@
         <v>900</v>
       </c>
       <c r="E44" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="F44" s="3">
         <v>500</v>
       </c>
       <c r="G44" s="3">
+        <v>500</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>800</v>
+      </c>
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>200</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
         <v>1100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3">
-        <v>500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="F45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="T45" s="3">
         <v>3100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>2300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
@@ -2806,176 +3212,200 @@
         <v>69700</v>
       </c>
       <c r="E46" s="3">
-        <v>62000</v>
+        <v>70100</v>
       </c>
       <c r="F46" s="3">
-        <v>61600</v>
+        <v>59900</v>
       </c>
       <c r="G46" s="3">
+        <v>58300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>69600</v>
+      </c>
+      <c r="I46" s="3">
+        <v>73400</v>
+      </c>
+      <c r="J46" s="3">
+        <v>65100</v>
+      </c>
+      <c r="K46" s="3">
         <v>63600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>67500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>24000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>17900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>14100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>13900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>13800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>15900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>18500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>13300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>10700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>9800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>10700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>12200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>10400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>3900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>4300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>4400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>4300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>4500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>4600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>300</v>
       </c>
-      <c r="Q47" s="3" t="s">
+      <c r="U47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H48" s="3">
         <v>3800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K48" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M48" s="3">
         <v>4300</v>
       </c>
-      <c r="F48" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>4800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>4500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>3900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>3700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>3500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>400</v>
-      </c>
-      <c r="T48" s="3">
-        <v>400</v>
       </c>
       <c r="U48" s="3">
         <v>400</v>
@@ -2983,8 +3413,20 @@
       <c r="V48" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>400</v>
+      </c>
+      <c r="X48" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2992,31 +3434,31 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>1500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>1800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>1900</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="J49" s="3">
-        <v>200</v>
-      </c>
-      <c r="K49" s="3">
-        <v>200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>200</v>
       </c>
       <c r="N49" s="3">
         <v>200</v>
@@ -3030,23 +3472,35 @@
       <c r="Q49" s="3">
         <v>200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>40</v>
+      <c r="R49" s="3">
+        <v>200</v>
+      </c>
+      <c r="S49" s="3">
+        <v>200</v>
+      </c>
+      <c r="T49" s="3">
+        <v>200</v>
+      </c>
+      <c r="U49" s="3">
+        <v>200</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3107,8 +3561,20 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3169,55 +3635,67 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E52" s="3">
-        <v>400</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3231,8 +3709,20 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3293,70 +3783,94 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>73500</v>
+        <v>76000</v>
       </c>
       <c r="E54" s="3">
-        <v>68300</v>
+        <v>76500</v>
       </c>
       <c r="F54" s="3">
-        <v>67700</v>
+        <v>68200</v>
       </c>
       <c r="G54" s="3">
+        <v>66200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>73300</v>
+      </c>
+      <c r="I54" s="3">
+        <v>77400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>71700</v>
+      </c>
+      <c r="K54" s="3">
         <v>70100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>78300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>32800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>26900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>22400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>22300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>22100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>19200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>20900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>15000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>11300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>10200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>11100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>12600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>11100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3379,8 +3893,12 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3403,353 +3921,417 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="U57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>2100</v>
-      </c>
-      <c r="U57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="E58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M58" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>1900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>2100</v>
       </c>
       <c r="R58" s="3">
         <v>1500</v>
       </c>
       <c r="S58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W58" s="3">
         <v>1100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="Y58" s="3">
         <v>1800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2500</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>1900</v>
+        <v>600</v>
       </c>
       <c r="F59" s="3">
         <v>2200</v>
       </c>
       <c r="G59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>2500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1300</v>
       </c>
       <c r="T59" s="3">
         <v>1700</v>
       </c>
       <c r="U59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F60" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H60" s="3">
         <v>8400</v>
       </c>
-      <c r="E60" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F60" s="3">
-        <v>7300</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K60" s="3">
         <v>7800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>10600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>14800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>9000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>7000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>6000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>5600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>4100</v>
-      </c>
-      <c r="O60" s="3">
-        <v>4100</v>
-      </c>
-      <c r="P60" s="3">
-        <v>5300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>5400</v>
-      </c>
-      <c r="R60" s="3">
-        <v>4200</v>
       </c>
       <c r="S60" s="3">
         <v>4100</v>
       </c>
       <c r="T60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="U60" s="3">
         <v>5400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>4400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E61" s="3">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="F61" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>1000</v>
       </c>
       <c r="K61" s="3">
+        <v>800</v>
+      </c>
+      <c r="L61" s="3">
+        <v>900</v>
+      </c>
+      <c r="M61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O61" s="3">
         <v>1100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>1200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>1400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>1400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="T61" s="3">
         <v>1400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3">
+        <v>100</v>
+      </c>
+      <c r="H62" s="3">
         <v>4400</v>
       </c>
-      <c r="E62" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K62" s="3">
         <v>6400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>27100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>40</v>
@@ -3757,17 +4339,17 @@
       <c r="P62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -3775,8 +4357,20 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3837,8 +4431,20 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3899,8 +4505,20 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3961,70 +4579,94 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11400</v>
+        <v>8500</v>
       </c>
       <c r="E66" s="3">
-        <v>12100</v>
+        <v>8500</v>
       </c>
       <c r="F66" s="3">
         <v>9600</v>
       </c>
       <c r="G66" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I66" s="3">
+        <v>13500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K66" s="3">
         <v>14000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>37500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>17100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>11700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>9600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>8700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>8400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>7200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>7200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>8200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>6800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>5400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>5300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>6600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>5600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4047,8 +4689,12 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4109,8 +4755,20 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4171,8 +4829,20 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4233,8 +4903,20 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4295,70 +4977,94 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-23000</v>
+        <v>-29700</v>
       </c>
       <c r="E72" s="3">
-        <v>-18900</v>
+        <v>-29900</v>
       </c>
       <c r="F72" s="3">
-        <v>-14800</v>
+        <v>-26600</v>
       </c>
       <c r="G72" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-12600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>-28000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>-26100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>-24900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>-23100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>-22800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>-20200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>-21300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>-18200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>-14200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>-13100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>-11400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>-10100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>-9500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-8700</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4419,8 +5125,20 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4481,8 +5199,20 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4543,70 +5273,94 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="E76" s="3">
-        <v>56200</v>
+        <v>69600</v>
       </c>
       <c r="F76" s="3">
-        <v>58100</v>
+        <v>60100</v>
       </c>
       <c r="G76" s="3">
+        <v>58400</v>
+      </c>
+      <c r="H76" s="3">
+        <v>61900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>65400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>58900</v>
+      </c>
+      <c r="K76" s="3">
         <v>56100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>40800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>15700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>15200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>12800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>13600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>13700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>12000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>13700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>6800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>4400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>4800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>5800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>6000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>5500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4667,137 +5421,173 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>43190</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>43008</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>42916</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>42825</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>42735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>42643</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-4000</v>
+        <v>-1900</v>
       </c>
       <c r="E81" s="3">
-        <v>-4100</v>
+        <v>-1900</v>
       </c>
       <c r="F81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="K81" s="3">
         <v>15400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4820,8 +5610,12 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4829,7 +5623,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -4847,31 +5641,31 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4882,8 +5676,20 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4944,8 +5750,20 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5006,8 +5824,20 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5068,8 +5898,20 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5130,8 +5972,20 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5192,70 +6046,94 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-3600</v>
+        <v>-2600</v>
       </c>
       <c r="E89" s="3">
-        <v>-3600</v>
+        <v>-2600</v>
       </c>
       <c r="F89" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="G89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-3800</v>
       </c>
       <c r="N89" s="3">
         <v>-800</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>900</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5278,59 +6156,63 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="N91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5340,8 +6222,20 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5402,8 +6296,20 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5464,70 +6370,94 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-29200</v>
+        <v>-4000</v>
       </c>
       <c r="E94" s="3">
-        <v>-4700</v>
+        <v>-4100</v>
       </c>
       <c r="F94" s="3">
-        <v>-3700</v>
+        <v>4300</v>
       </c>
       <c r="G94" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K94" s="3">
         <v>3700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5550,31 +6480,35 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5612,8 +6546,20 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5674,8 +6620,20 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5736,8 +6694,20 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5798,118 +6768,142 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7600</v>
+        <v>5300</v>
       </c>
       <c r="E100" s="3">
-        <v>200</v>
+        <v>5300</v>
       </c>
       <c r="F100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>100</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L100" s="3">
+        <v>46700</v>
+      </c>
+      <c r="M100" s="3">
+        <v>7800</v>
+      </c>
+      <c r="N100" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O100" s="3">
+        <v>300</v>
+      </c>
+      <c r="P100" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>100</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="U100" s="3">
+        <v>800</v>
+      </c>
+      <c r="V100" s="3">
+        <v>400</v>
+      </c>
+      <c r="W100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>46700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>7800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>8000</v>
-      </c>
-      <c r="P100" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>800</v>
-      </c>
-      <c r="R100" s="3">
-        <v>400</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="E101" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F101" s="3">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="G101" s="3">
+        <v>700</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -5922,66 +6916,90 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-22800</v>
+        <v>-800</v>
       </c>
       <c r="E102" s="3">
-        <v>-6600</v>
+        <v>-800</v>
       </c>
       <c r="F102" s="3">
-        <v>-2100</v>
+        <v>1200</v>
       </c>
       <c r="G102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>37700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>5600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>RCON</t>
   </si>
@@ -656,341 +656,366 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43190</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43008</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42825</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42643</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>5900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>5500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3100</v>
-      </c>
-      <c r="M9" s="3">
-        <v>2500</v>
-      </c>
-      <c r="N9" s="3">
-        <v>3800</v>
       </c>
       <c r="O9" s="3">
         <v>2500</v>
       </c>
       <c r="P9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>5700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-600</v>
-      </c>
-      <c r="S10" s="3">
-        <v>300</v>
-      </c>
-      <c r="T10" s="3">
-        <v>600</v>
       </c>
       <c r="U10" s="3">
         <v>300</v>
       </c>
       <c r="V10" s="3">
+        <v>600</v>
+      </c>
+      <c r="W10" s="3">
+        <v>300</v>
+      </c>
+      <c r="X10" s="3">
         <v>100</v>
-      </c>
-      <c r="W10" s="3">
-        <v>200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1400</v>
       </c>
       <c r="Y10" s="3">
         <v>200</v>
       </c>
       <c r="Z10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1017,16 +1042,18 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E12" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F12" s="3">
         <v>500</v>
@@ -1035,43 +1062,43 @@
         <v>500</v>
       </c>
       <c r="H12" s="3">
+        <v>500</v>
+      </c>
+      <c r="I12" s="3">
+        <v>500</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
-      </c>
-      <c r="S12" s="3">
-        <v>100</v>
-      </c>
-      <c r="T12" s="3">
-        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>100</v>
@@ -1080,19 +1107,25 @@
         <v>200</v>
       </c>
       <c r="W12" s="3">
+        <v>100</v>
+      </c>
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z12" s="3">
         <v>600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1165,8 +1198,14 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,26 +1221,26 @@
       <c r="G14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="3">
-        <v>100</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>40</v>
+      <c r="N14" s="3">
+        <v>100</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>40</v>
@@ -1215,11 +1254,11 @@
       <c r="R14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1239,8 +1278,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1266,10 +1311,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1313,8 +1358,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1389,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F17" s="3">
         <v>5000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>12700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>10400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>10700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="X17" s="3">
-        <v>5000</v>
       </c>
       <c r="Y17" s="3">
         <v>1900</v>
       </c>
       <c r="Z17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-2100</v>
       </c>
       <c r="W18" s="3">
         <v>-1000</v>
       </c>
       <c r="X18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1514,62 +1579,64 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>20700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1588,82 +1655,94 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>15700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1674,31 +1753,31 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
       <c r="L22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1713,10 +1792,10 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1736,82 +1815,94 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2300</v>
       </c>
       <c r="J23" s="3">
         <v>-2200</v>
       </c>
       <c r="K23" s="3">
-        <v>15400</v>
+        <v>-2300</v>
       </c>
       <c r="L23" s="3">
         <v>-2200</v>
       </c>
       <c r="M23" s="3">
+        <v>15400</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-2100</v>
       </c>
       <c r="W23" s="3">
         <v>-1000</v>
       </c>
       <c r="X23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1840,26 +1931,26 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1884,8 +1975,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1958,156 +2055,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2300</v>
       </c>
       <c r="J26" s="3">
         <v>-2200</v>
       </c>
       <c r="K26" s="3">
-        <v>15400</v>
+        <v>-2300</v>
       </c>
       <c r="L26" s="3">
         <v>-2200</v>
       </c>
       <c r="M26" s="3">
+        <v>15400</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>15400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2180,8 +2295,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2254,8 +2375,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2328,8 +2455,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2402,62 +2535,68 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-20700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
-      </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2476,82 +2615,94 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>15400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2624,161 +2775,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>15400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43190</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43008</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42825</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42643</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2805,8 +2974,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2833,111 +3004,119 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F41" s="3">
         <v>15100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>16700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>14400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>39000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>46000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>47500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>12100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>12200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>18900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>18400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>25400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>26800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>40</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>40</v>
@@ -2945,11 +3124,11 @@
       <c r="N42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2981,304 +3160,334 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F43" s="3">
         <v>41400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>41700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>23200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>22500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>28400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>30000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>25100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>16900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>19200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>13900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>12400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>12800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>7400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>6900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>8400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>6800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>7100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>8600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>10500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>8800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>200</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
         <v>1100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>700</v>
-      </c>
-      <c r="V44" s="3">
-        <v>400</v>
-      </c>
-      <c r="W44" s="3">
-        <v>400</v>
       </c>
       <c r="X44" s="3">
         <v>400</v>
       </c>
       <c r="Y44" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA44" s="3">
         <v>900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>600</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>4700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>68300</v>
+      </c>
+      <c r="F46" s="3">
         <v>69700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>70100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>59900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>58300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>69600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>73400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>65100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>63600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>67500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>24000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>17900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>14100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>13900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>13800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>15900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>18500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>13300</v>
-      </c>
-      <c r="U46" s="3">
-        <v>10700</v>
-      </c>
-      <c r="V46" s="3">
-        <v>9800</v>
       </c>
       <c r="W46" s="3">
         <v>10700</v>
       </c>
       <c r="X46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="Z46" s="3">
         <v>12200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>10400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -3303,115 +3512,121 @@
       <c r="J47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>3900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>4300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>4400</v>
       </c>
       <c r="O47" s="3">
         <v>4300</v>
       </c>
       <c r="P47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>4300</v>
+      </c>
+      <c r="R47" s="3">
         <v>4500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>300</v>
       </c>
-      <c r="U47" s="3" t="s">
+      <c r="W47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
         <v>300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G48" s="3">
         <v>6400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
-      </c>
-      <c r="U48" s="3">
-        <v>400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>400</v>
@@ -3425,8 +3640,14 @@
       <c r="Z48" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3449,22 +3670,22 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>1500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1900</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="O49" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="N49" s="3">
-        <v>200</v>
-      </c>
-      <c r="O49" s="3">
-        <v>200</v>
       </c>
       <c r="P49" s="3">
         <v>200</v>
@@ -3484,11 +3705,11 @@
       <c r="U49" s="3">
         <v>200</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>40</v>
+      <c r="V49" s="3">
+        <v>200</v>
+      </c>
+      <c r="W49" s="3">
+        <v>200</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>40</v>
@@ -3499,8 +3720,14 @@
       <c r="Z49" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3800,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,8 +3880,14 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3664,29 +3903,29 @@
       <c r="G52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>40</v>
+      <c r="N52" s="3">
+        <v>200</v>
+      </c>
+      <c r="O52" s="3">
+        <v>200</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>40</v>
@@ -3697,11 +3936,11 @@
       <c r="R52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3721,8 +3960,14 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,82 +4040,94 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>77200</v>
+      </c>
+      <c r="F54" s="3">
         <v>76000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>76500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>68200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>66200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>73300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>77400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>71700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>70100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>78300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>32800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>26900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>22400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>22300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>22100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>19200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>20900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>11300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>10200</v>
-      </c>
-      <c r="W54" s="3">
-        <v>11100</v>
-      </c>
-      <c r="X54" s="3">
-        <v>12600</v>
       </c>
       <c r="Y54" s="3">
         <v>11100</v>
       </c>
       <c r="Z54" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>11100</v>
+      </c>
+      <c r="AB54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4154,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,319 +4184,345 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2300</v>
-      </c>
-      <c r="U57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="V57" s="3">
-        <v>1200</v>
       </c>
       <c r="W57" s="3">
         <v>1600</v>
       </c>
       <c r="X57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z57" s="3">
         <v>2100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="E58" s="3">
         <v>3600</v>
       </c>
       <c r="F58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H58" s="3">
         <v>4700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>9300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>900</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>4400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -4245,43 +4530,43 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1200</v>
-      </c>
-      <c r="R61" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S61" s="3">
-        <v>1400</v>
       </c>
       <c r="T61" s="3">
         <v>1400</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -4295,8 +4580,14 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4307,37 +4598,37 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>27100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>200</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>40</v>
@@ -4351,11 +4642,11 @@
       <c r="T62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4369,8 +4660,14 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4740,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4517,8 +4820,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,82 +4900,94 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F66" s="3">
         <v>8500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>37500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>17100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>7200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>6800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>5600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +5014,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +5090,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5170,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4915,8 +5250,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,82 +5330,94 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-29700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-29900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-25900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-22900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-24200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-19900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-12600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-28000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-26100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-24900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-23100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-20200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-21300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-18200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-16500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-14200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-13100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-11400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-8700</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5490,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5570,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,82 +5650,94 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>69200</v>
+        <v>66900</v>
       </c>
       <c r="E76" s="3">
         <v>69600</v>
       </c>
       <c r="F76" s="3">
+        <v>69200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>69600</v>
+      </c>
+      <c r="H76" s="3">
         <v>60100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>58400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>61900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>65400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>58900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>56100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>40800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>12800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13600</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>13700</v>
-      </c>
-      <c r="R76" s="3">
-        <v>12000</v>
       </c>
       <c r="S76" s="3">
         <v>13700</v>
       </c>
       <c r="T76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="U76" s="3">
+        <v>13700</v>
+      </c>
+      <c r="V76" s="3">
         <v>6800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>5800</v>
-      </c>
-      <c r="X76" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>5500</v>
       </c>
       <c r="Z76" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5810,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43190</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43008</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42825</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42643</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>15400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,16 +6009,18 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -5653,16 +6050,16 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -5671,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5688,8 +6085,14 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +6165,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6245,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6325,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6405,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6485,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-1700</v>
       </c>
       <c r="U89" s="3">
         <v>-300</v>
       </c>
       <c r="V89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>900</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,65 +6599,67 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F91" s="3">
         <v>1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -6234,8 +6675,14 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6755,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,71 +6835,77 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>4300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>4200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-14600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-15400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>3700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -6456,8 +6915,14 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,8 +6949,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6510,11 +6977,11 @@
       <c r="J96" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6558,8 +7025,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +7105,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +7185,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,136 +7265,148 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>5300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>5300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>46700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>7800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -6928,78 +7425,90 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-12000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>37700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>5600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-4600</v>
       </c>
       <c r="R102" s="3">
         <v>-1100</v>
       </c>
       <c r="S102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="T102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="U102" s="3">
         <v>6800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>RCON</t>
   </si>
@@ -656,392 +656,417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42825</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42643</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>8500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>5500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3100</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>2500</v>
-      </c>
-      <c r="R9" s="3">
-        <v>3800</v>
       </c>
       <c r="S9" s="3">
         <v>2500</v>
       </c>
       <c r="T9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="V9" s="3">
         <v>6500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>5700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>3000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-600</v>
-      </c>
-      <c r="W10" s="3">
-        <v>300</v>
-      </c>
-      <c r="X10" s="3">
-        <v>600</v>
       </c>
       <c r="Y10" s="3">
         <v>300</v>
       </c>
       <c r="Z10" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB10" s="3">
         <v>100</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1400</v>
       </c>
       <c r="AC10" s="3">
         <v>200</v>
       </c>
       <c r="AD10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1072,28 +1097,30 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>600</v>
+      </c>
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>500</v>
       </c>
       <c r="J12" s="3">
         <v>500</v>
@@ -1102,43 +1129,43 @@
         <v>500</v>
       </c>
       <c r="L12" s="3">
+        <v>500</v>
+      </c>
+      <c r="M12" s="3">
+        <v>500</v>
+      </c>
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>200</v>
       </c>
       <c r="Y12" s="3">
         <v>100</v>
@@ -1147,19 +1174,25 @@
         <v>200</v>
       </c>
       <c r="AA12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD12" s="3">
         <v>600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1244,16 +1277,22 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>40</v>
+      <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>40</v>
@@ -1273,26 +1312,26 @@
       <c r="K14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P14" s="3">
-        <v>100</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>40</v>
+      <c r="R14" s="3">
+        <v>100</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>40</v>
@@ -1306,11 +1345,11 @@
       <c r="V14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1330,8 +1369,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1369,10 +1414,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1416,8 +1461,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1445,180 +1496,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F17" s="3">
         <v>3800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>12700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>10400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>10700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>7100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>7900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4400</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>5000</v>
       </c>
       <c r="AC17" s="3">
         <v>1900</v>
       </c>
       <c r="AD17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AF17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1600</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-2100</v>
       </c>
       <c r="AA18" s="3">
         <v>-1000</v>
       </c>
       <c r="AB18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1649,74 +1714,76 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>20700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>5200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1735,94 +1802,106 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>15700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1845,31 +1924,31 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
-      </c>
       <c r="P22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1884,10 +1963,10 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1907,94 +1986,106 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-2300</v>
       </c>
       <c r="N23" s="3">
         <v>-2200</v>
       </c>
       <c r="O23" s="3">
-        <v>15400</v>
+        <v>-2300</v>
       </c>
       <c r="P23" s="3">
         <v>-2200</v>
       </c>
       <c r="Q23" s="3">
+        <v>15400</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-2100</v>
       </c>
       <c r="AA23" s="3">
         <v>-1000</v>
       </c>
       <c r="AB23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2035,26 +2126,26 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -2079,8 +2170,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2165,180 +2262,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-2300</v>
       </c>
       <c r="N26" s="3">
         <v>-2200</v>
       </c>
       <c r="O26" s="3">
-        <v>15400</v>
+        <v>-2300</v>
       </c>
       <c r="P26" s="3">
         <v>-2200</v>
       </c>
       <c r="Q26" s="3">
+        <v>15400</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-1400</v>
       </c>
       <c r="G27" s="3">
         <v>-1500</v>
       </c>
       <c r="H27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>15400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2423,8 +2538,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2509,8 +2630,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2595,8 +2722,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2681,74 +2814,80 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-20700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
-      </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2767,94 +2906,106 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-1400</v>
       </c>
       <c r="G33" s="3">
         <v>-1500</v>
       </c>
       <c r="H33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>15400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2939,185 +3090,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-1400</v>
       </c>
       <c r="G35" s="3">
         <v>-1500</v>
       </c>
       <c r="H35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>15400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42825</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42643</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3148,8 +3317,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3180,135 +3351,143 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F41" s="3">
         <v>13800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>15100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>16700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>39000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>46000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>47500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>7200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>8100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>500</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>12100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>12200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>18900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>18400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>25400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>26800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>40</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>40</v>
@@ -3316,11 +3495,11 @@
       <c r="R42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3352,360 +3531,390 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F43" s="3">
         <v>32500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>32000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>43600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>45400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>41100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>41300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>23200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>22500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>28400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>30000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>25100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>16900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>19200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>13900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>13300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>12400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>12800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>5600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>6900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>8400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>6800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>7100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>8600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>10500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>8800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>200</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
         <v>1100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>700</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>400</v>
       </c>
       <c r="AB44" s="3">
         <v>400</v>
       </c>
       <c r="AC44" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE44" s="3">
         <v>900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>4700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>48500</v>
+      </c>
+      <c r="F46" s="3">
         <v>49700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>49100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>65700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>68300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>69700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>70100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>59900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>58300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>69600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>73400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>65100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>63600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>67500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>24000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>17900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>14100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>13900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>13800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>15900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>13300</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>10700</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>9800</v>
       </c>
       <c r="AA46" s="3">
         <v>10700</v>
       </c>
       <c r="AB46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="AD46" s="3">
         <v>12200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>10400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>40</v>
+      <c r="D47" s="3">
+        <v>200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>200</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>40</v>
@@ -3734,127 +3943,133 @@
       <c r="N47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>4300</v>
-      </c>
-      <c r="R47" s="3">
-        <v>4400</v>
       </c>
       <c r="S47" s="3">
         <v>4300</v>
       </c>
       <c r="T47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U47" s="3">
+        <v>4300</v>
+      </c>
+      <c r="V47" s="3">
         <v>4500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>4600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>300</v>
       </c>
-      <c r="Y47" s="3" t="s">
+      <c r="AA47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
         <v>300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F48" s="3">
         <v>7100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>400</v>
       </c>
       <c r="AA48" s="3">
         <v>400</v>
@@ -3868,8 +4083,14 @@
       <c r="AD48" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3904,22 +4125,22 @@
         <v>0</v>
       </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>1500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1900</v>
       </c>
-      <c r="Q49" s="3" t="s">
+      <c r="S49" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="R49" s="3">
-        <v>200</v>
-      </c>
-      <c r="S49" s="3">
-        <v>200</v>
       </c>
       <c r="T49" s="3">
         <v>200</v>
@@ -3939,11 +4160,11 @@
       <c r="Y49" s="3">
         <v>200</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA49" s="3" t="s">
-        <v>40</v>
+      <c r="Z49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>200</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>40</v>
@@ -3954,8 +4175,14 @@
       <c r="AD49" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4040,8 +4267,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4126,8 +4359,14 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4155,29 +4394,29 @@
       <c r="K52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>40</v>
+      <c r="R52" s="3">
+        <v>200</v>
+      </c>
+      <c r="S52" s="3">
+        <v>200</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>40</v>
@@ -4188,11 +4427,11 @@
       <c r="V52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4212,8 +4451,14 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4298,94 +4543,106 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>76300</v>
+      </c>
+      <c r="F54" s="3">
         <v>73400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>72400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>74200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>77200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>76000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>76500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>68200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>66200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>73300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>77400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>71700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>70100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>78300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>32800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>26900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>22400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>22300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>22100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>19200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>20900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>15000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>11300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>10200</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>11100</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>12600</v>
       </c>
       <c r="AC54" s="3">
         <v>11100</v>
       </c>
       <c r="AD54" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AE54" s="3">
+        <v>11100</v>
+      </c>
+      <c r="AF54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4416,8 +4673,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4448,352 +4707,378 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>1200</v>
       </c>
       <c r="AA57" s="3">
         <v>1600</v>
       </c>
       <c r="AB57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD57" s="3">
         <v>2100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F58" s="3">
         <v>3300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>3600</v>
       </c>
       <c r="I58" s="3">
         <v>3600</v>
       </c>
       <c r="J58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>9300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F60" s="3">
         <v>8500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>10600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>9000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>7000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>5400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4804,23 +5089,23 @@
         <v>1500</v>
       </c>
       <c r="F61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H61" s="3">
         <v>1800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4828,43 +5113,43 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1200</v>
-      </c>
-      <c r="V61" s="3">
-        <v>1400</v>
-      </c>
-      <c r="W61" s="3">
-        <v>1400</v>
       </c>
       <c r="X61" s="3">
         <v>1400</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -4878,16 +5163,22 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -4902,37 +5193,37 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>6400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>27100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>200</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>40</v>
@@ -4946,11 +5237,11 @@
       <c r="X62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4964,8 +5255,14 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5050,8 +5347,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5136,8 +5439,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5222,94 +5531,106 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F66" s="3">
         <v>10000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>9300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>14000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>37500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>17100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>11700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>7200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>7200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>6800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>6600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>5600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5340,8 +5661,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5426,8 +5749,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5512,8 +5841,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5598,8 +5933,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5684,94 +6025,106 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-36100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-35700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-32400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-33800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-29700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-29900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-26600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-25900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-22900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-24200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-19900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-12600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-26100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-24900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-23100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-22800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-20200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-21300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-18200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-11400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-8700</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5856,8 +6209,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5942,8 +6301,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6028,94 +6393,106 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E76" s="3">
         <v>65200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>65200</v>
+      </c>
+      <c r="G76" s="3">
         <v>64400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>66900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>69600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>69200</v>
       </c>
       <c r="I76" s="3">
         <v>69600</v>
       </c>
       <c r="J76" s="3">
+        <v>69200</v>
+      </c>
+      <c r="K76" s="3">
+        <v>69600</v>
+      </c>
+      <c r="L76" s="3">
         <v>60100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>58400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>61900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>65400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>58900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>56100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>40800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>15700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>15200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>12800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13600</v>
-      </c>
-      <c r="U76" s="3">
-        <v>13700</v>
-      </c>
-      <c r="V76" s="3">
-        <v>12000</v>
       </c>
       <c r="W76" s="3">
         <v>13700</v>
       </c>
       <c r="X76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Y76" s="3">
+        <v>13700</v>
+      </c>
+      <c r="Z76" s="3">
         <v>6800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5800</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>5500</v>
       </c>
       <c r="AD76" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AF76" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6200,185 +6577,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42825</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42643</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-1400</v>
       </c>
       <c r="G81" s="3">
         <v>-1500</v>
       </c>
       <c r="H81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>15400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6409,8 +6804,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6421,16 +6818,16 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>200</v>
+      </c>
+      <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -6460,16 +6857,16 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -6478,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6495,8 +6892,14 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6581,8 +6984,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6667,8 +7076,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6753,8 +7168,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6839,8 +7260,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6925,94 +7352,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-1700</v>
       </c>
       <c r="Y89" s="3">
         <v>-300</v>
       </c>
       <c r="Z89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>900</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7043,77 +7482,79 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -7129,8 +7570,14 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7215,8 +7662,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7301,83 +7754,89 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>3400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>4300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>4200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-14600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-15400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -7387,8 +7846,14 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7419,8 +7884,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7457,11 +7924,11 @@
       <c r="N96" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7505,8 +7972,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7591,8 +8064,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7677,8 +8156,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7763,16 +8248,22 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="E100" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
@@ -7781,142 +8272,148 @@
         <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>5300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>5300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>4000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>46700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>7800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>4300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>2900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -7935,90 +8432,102 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-11400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>37700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>5600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-4600</v>
       </c>
       <c r="V102" s="3">
         <v>-1100</v>
       </c>
       <c r="W102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="X102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
     </row>
